--- a/artfynd/A 36983-2025 artfynd.xlsx
+++ b/artfynd/A 36983-2025 artfynd.xlsx
@@ -675,55 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104862640</v>
+        <v>126379693</v>
       </c>
       <c r="B2" t="n">
-        <v>12249</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101283</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Marsjärv, nyckelbiotop SV om, Nb</t>
+          <t>Marsjärv, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>821540.6071516636</v>
+        <v>821534</v>
       </c>
       <c r="R2" t="n">
-        <v>7387799.354421686</v>
+        <v>7387822</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sannolika kläckhål och larvgnag, men svårt att se eftersom det är gammalt</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,79 +766,64 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lövrik barrblandskog på frisk - fuktig mark</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Glasbjörkstubbe 22 cm med både levande och döda fnösketickor</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av vedlevande evertebrater</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104862641</v>
+        <v>126379696</v>
       </c>
       <c r="B3" t="n">
-        <v>18534</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101797</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Karelsk barkfluga</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Xylomya czekanovskii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pleske, 1925</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Marsjärv, nyckelbiotop SV om, Nb</t>
+          <t>Marsjärv, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>821536.1067428847</v>
+        <v>821530</v>
       </c>
       <c r="R3" t="n">
-        <v>7387695.555612344</v>
+        <v>7387828</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,27 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>en enda lämplig asplåga i området</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,78 +872,65 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Lövrik barrblandskog på frisk - fuktig mark</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Avbruten asp 65 cm, bitvis med slaskbark</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av vedlevande evertebrater</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126379696</v>
+        <v>104862640</v>
       </c>
       <c r="B4" t="n">
-        <v>91245</v>
+        <v>12364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>101283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Schaller, 1783)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Marsjärv, Nb</t>
+          <t>Marsjärv, nyckelbiotop SV om, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>821530</v>
+        <v>821541</v>
       </c>
       <c r="R4" t="n">
-        <v>7387828</v>
+        <v>7387799</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,17 +957,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Sannolika kläckhål och larvgnag, men svårt att se eftersom det är gammalt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,64 +979,74 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Lövrik barrblandskog på frisk - fuktig mark</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Glasbjörkstubbe 22 cm med både levande och döda fnösketickor</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av vedlevande evertebrater</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126379693</v>
+        <v>104862638</v>
       </c>
       <c r="B5" t="n">
-        <v>91541</v>
+        <v>57774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>102976</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Marsjärv, Nb</t>
+          <t>Marsjärv, nyckelbiotop SV om, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>821534</v>
+        <v>821512</v>
       </c>
       <c r="R5" t="n">
-        <v>7387822</v>
+        <v>7387704</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,17 +1073,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>3 ex flygande längs vägen mitt i nyckelbiotop, bor säkert i gammelasparna</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,18 +1095,27 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Lövrik barrblandskog på frisk - fuktig mark</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av vedlevande evertebrater</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
